--- a/data/trans_bre/P32C-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P32C-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,02</t>
+          <t>-1,93; 2,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,6; -1,25</t>
+          <t>-5,5; -1,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,0</t>
+          <t>-2,5; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 2,1</t>
+          <t>-0,6; 2,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,37</t>
+          <t>-2,39; 1,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,37; -0,43</t>
+          <t>-5,41; -0,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,96; -0,44</t>
+          <t>-4,3; -0,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,97; -0,15</t>
+          <t>-2,78; -0,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; -0,58</t>
+          <t>-3,19; -0,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; -0,27</t>
+          <t>-2,77; -0,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 7,73</t>
+          <t>-1,66; 8,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; -0,34</t>
+          <t>-3,52; -0,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,75</t>
+          <t>-3,32; 0,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -0,08</t>
+          <t>-2,89; -0,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,45</t>
+          <t>-2,71; 0,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,33</t>
+          <t>-2,21; 0,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 98,35</t>
+          <t>-100,0; 90,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 92,96</t>
+          <t>-100,0; 63,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 109,75</t>
+          <t>-100,0; 91,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 58,05</t>
+          <t>-100,0; 69,32</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,45</t>
+          <t>-4,05; 2,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,69; -0,5</t>
+          <t>-4,57; -0,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,63; -1,11</t>
+          <t>-4,88; -1,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 1,06</t>
+          <t>-4,29; 0,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 386,28</t>
+          <t>-100,0; 352,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 64,06</t>
+          <t>-100,0; 82,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-88,75; 93,96</t>
+          <t>-89,89; 75,11</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,86</t>
+          <t>-1,79; 1,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,79</t>
+          <t>-3,66; 0,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 1,84</t>
+          <t>-2,52; 1,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,41</t>
+          <t>0,0; 9,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,14</t>
+          <t>-1,87; 0,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; -1,02</t>
+          <t>-2,49; -1,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; -0,34</t>
+          <t>-1,81; -0,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,53</t>
+          <t>-1,2; 0,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-80,2; 16,25</t>
+          <t>-83,62; 3,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-96,4; -56,98</t>
+          <t>-96,09; -53,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-86,38; -18,69</t>
+          <t>-89,0; -20,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-78,14; 61,43</t>
+          <t>-78,05; 59,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32C-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P32C-Clase-trans_bre.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>157,64%</t>
+          <t>171,28%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,02</t>
+          <t>-2,07; 2,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; -1,27</t>
+          <t>-5,47; -1,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 0,0</t>
+          <t>-2,42; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,17</t>
+          <t>-0,29; 2,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-1,14</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,36</t>
+          <t>-2,41; 1,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,41; -0,57</t>
+          <t>-5,24; -0,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,3; -0,45</t>
+          <t>-4,78; -0,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,78; -0,08</t>
+          <t>-3,0; -0,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,16</t>
+          <t>-1,08</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,55</t>
+          <t>-3,17; -0,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; -0,32</t>
+          <t>-2,55; -0,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 8,24</t>
+          <t>-1,73; 8,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; -0,33</t>
+          <t>-3,07; -0,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-61,19%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,62</t>
+          <t>-3,16; 1,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,89; -0,18</t>
+          <t>-3,01; -0,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,29</t>
+          <t>-2,54; 0,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,31</t>
+          <t>-1,0; 4,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 90,22</t>
+          <t>-100,0; 112,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 63,27</t>
+          <t>-100,0; 66,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 91,8</t>
+          <t>-100,0; 123,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 69,32</t>
+          <t>-79,8; 644,73</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-1,41</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-49,11%</t>
+          <t>-49,91%</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 2,86</t>
+          <t>-3,94; 3,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,57; -0,35</t>
+          <t>-4,73; -0,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -1,08</t>
+          <t>-4,66; -0,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 0,98</t>
+          <t>-4,0; 0,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 352,46</t>
+          <t>-100,0; 271,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 82,97</t>
+          <t>-100,0; 19,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,14 +1095,14 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-89,89; 75,11</t>
+          <t>-88,0; 85,48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>1,76</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,87</t>
+          <t>-2,11; 1,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 0,79</t>
+          <t>-4,05; 0,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,83</t>
+          <t>-2,38; 1,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,39</t>
+          <t>0,0; 9,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-37,55%</t>
+          <t>-6,5%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,01</t>
+          <t>-1,87; -0,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; -1,02</t>
+          <t>-2,62; -1,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,81; -0,34</t>
+          <t>-1,91; -0,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,47</t>
+          <t>-0,84; 1,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-83,62; 3,6</t>
+          <t>-80,72; 4,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-96,09; -53,79</t>
+          <t>-100,0; -55,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-89,0; -20,05</t>
+          <t>-89,92; -23,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-78,05; 59,89</t>
+          <t>-58,41; 139,44</t>
         </is>
       </c>
     </row>
